--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -79,13 +79,70 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
     <t>VALLEJO</t>
   </si>
   <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>JUAN EMANUEL</t>
+  </si>
+  <si>
     <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>LUZ ARELY</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>ADAMARI</t>
+  </si>
+  <si>
+    <t>NORMA ANGELICA</t>
   </si>
 </sst>
 </file>
@@ -935,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -967,25 +1024,186 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920394</v>
+        <v>22330051920230</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920233</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920401</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920394</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330061460173</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920240</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920375</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330061460548</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
     <t>APARICIO</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>VALLEJO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
@@ -131,6 +137,9 @@
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>LESLIE YAMILET</t>
   </si>
   <si>
     <t>LUZ ARELY</t>
@@ -992,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1030,10 +1039,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1053,10 +1062,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1076,10 +1085,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1099,10 +1108,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1116,39 +1125,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330061460173</v>
+        <v>22330051920417</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920240</v>
+        <v>22330061460173</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1162,16 +1171,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920375</v>
+        <v>22330051920240</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1185,16 +1194,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330061460548</v>
+        <v>22330051920375</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1203,6 +1212,29 @@
         <v>10</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330061460548</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -575,7 +575,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -584,13 +584,13 @@
         <v>19</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>54.76</v>
+        <v>53.66</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -741,13 +741,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -907,13 +907,13 @@
         <v>19</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>54.76</v>
+        <v>53.66</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -79,18 +79,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
     <t>BONILLA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>LIBRADO</t>
   </si>
   <si>
@@ -103,12 +100,12 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t>PULIDO</t>
   </si>
   <si>
@@ -118,21 +115,18 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>AZURA</t>
-  </si>
-  <si>
     <t>FERNANDA MARGARITA</t>
   </si>
   <si>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
     <t>JUAN EMANUEL</t>
   </si>
   <si>
@@ -143,9 +137,6 @@
   </si>
   <si>
     <t>LUZ ARELY</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
   </si>
   <si>
     <t>ADAMARI</t>
@@ -627,10 +618,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -639,7 +630,7 @@
         <v>28</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -787,10 +778,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -950,10 +941,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -962,7 +953,7 @@
         <v>28</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -1001,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1033,16 +1024,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920230</v>
+        <v>22330051920233</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1056,16 +1047,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920233</v>
+        <v>22330051920240</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1085,10 +1076,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1105,13 +1096,13 @@
         <v>22330051920394</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1128,13 +1119,13 @@
         <v>22330051920417</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1151,13 +1142,13 @@
         <v>22330061460173</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1171,16 +1162,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920240</v>
+        <v>22330051920375</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1194,16 +1185,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920375</v>
+        <v>22330061460548</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1212,29 +1203,6 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330061460548</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -79,70 +79,70 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>PULIDO</t>
   </si>
   <si>
-    <t>VALLEJO</t>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
   </si>
   <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>LESLIE YAMILET</t>
-  </si>
-  <si>
-    <t>LUZ ARELY</t>
-  </si>
-  <si>
-    <t>ADAMARI</t>
-  </si>
-  <si>
-    <t>NORMA ANGELICA</t>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
   </si>
 </sst>
 </file>
@@ -621,16 +621,16 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -712,16 +712,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>61.29</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -735,16 +738,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>73.17</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -758,16 +764,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>76.67</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -781,16 +790,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -804,16 +816,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H6">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -869,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>64.52</v>
+        <v>61.29</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -895,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>53.66</v>
+        <v>73.17</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -921,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>76.67</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -944,16 +959,16 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>84.84999999999999</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -973,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>90.91</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1024,7 +1039,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920233</v>
+        <v>22330051920369</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -1047,7 +1062,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920240</v>
+        <v>22330051920401</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1070,10 +1085,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920401</v>
+        <v>22330051920374</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>29</v>
@@ -1085,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1093,10 +1108,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920394</v>
+        <v>22330051920222</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
@@ -1116,7 +1131,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920417</v>
+        <v>22330051920302</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1139,13 +1154,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330061460173</v>
+        <v>22330051920303</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
@@ -1154,21 +1169,21 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920375</v>
+        <v>22330051920308</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
@@ -1177,15 +1192,15 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330061460548</v>
+        <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1200,7 +1215,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>1</v>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -79,70 +79,82 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>VALENTE</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>SILVESTRE</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
+    <t>ROCHA</t>
   </si>
   <si>
     <t>PULIDO</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>JORGE</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>OLIVARES</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
+    <t>AZURA</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
   </si>
   <si>
+    <t>ASHLEY</t>
+  </si>
+  <si>
     <t>KARLA YARITZY</t>
   </si>
   <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>EVELYN ROSALIA</t>
   </si>
   <si>
-    <t>ABDIEL ARMANDO</t>
+    <t>MICHELLE</t>
   </si>
   <si>
     <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,16 +1051,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920369</v>
+        <v>22330051920230</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1068,10 +1080,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1085,16 +1097,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920374</v>
+        <v>22321052600528</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1108,16 +1120,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920222</v>
+        <v>22330051920374</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1134,13 +1146,13 @@
         <v>22330051920302</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1154,16 +1166,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920303</v>
+        <v>22330051920308</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1177,25 +1189,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920308</v>
+        <v>22330051920222</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1203,13 +1215,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1218,6 +1230,29 @@
         <v>12</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920303</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,12 @@
     <t>VALENTE</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -97,28 +103,31 @@
     <t>PANTOJA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>SILVESTRE</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ROCHA</t>
   </si>
   <si>
     <t>PULIDO</t>
   </si>
   <si>
+    <t>SOTO</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
     <t>JORGE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>TELLEZ</t>
   </si>
   <si>
     <t>PALACIOS</t>
@@ -136,6 +145,12 @@
     <t>JUAN EMANUEL</t>
   </si>
   <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
     <t>ASHLEY</t>
   </si>
   <si>
@@ -146,6 +161,9 @@
   </si>
   <si>
     <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>EVELYN ROSALIA</t>
@@ -1019,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1057,10 +1075,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1080,10 +1098,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1097,22 +1115,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22321052600528</v>
+        <v>21330051920396</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1120,22 +1138,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920374</v>
+        <v>22330051920405</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1143,22 +1161,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920302</v>
+        <v>22321052600528</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1166,22 +1184,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920308</v>
+        <v>22330051920374</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1189,53 +1207,53 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920222</v>
+        <v>22330051920302</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920224</v>
+        <v>22330051920308</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920303</v>
+        <v>22330051920408</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1244,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1253,6 +1271,75 @@
         <v>13</v>
       </c>
       <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920222</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920224</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920303</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,100 +79,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ZAVALA</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
+    <t>DELGADO</t>
   </si>
   <si>
     <t>ROCHA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>PULIDO</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
+    <t>AXEL GAEL</t>
   </si>
   <si>
     <t>AZURA</t>
   </si>
   <si>
+    <t>HAZEL</t>
+  </si>
+  <si>
     <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>ASHLEY</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -914,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>61.29</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -966,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>76.67</v>
+        <v>86.67</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -992,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>78.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1018,16 +958,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>81.81999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1069,16 +1009,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920230</v>
+        <v>22330051920176</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1092,16 +1032,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920401</v>
+        <v>22330051920230</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1110,236 +1050,52 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920396</v>
+        <v>22330051920368</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920405</v>
+        <v>22330051920401</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22321052600528</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920374</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920302</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920308</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920408</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920222</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920224</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920303</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -82,37 +82,10 @@
     <t>ZAVALA</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
     <t>DELGADO</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
     <t>AXEL GAEL</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>HAZEL</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
   </si>
 </sst>
 </file>
@@ -880,16 +853,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>73.17</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -977,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1015,10 +988,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1028,75 +1001,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920230</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920368</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920401</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
